--- a/EndResult/200m Rygg.xlsx
+++ b/EndResult/200m Rygg.xlsx
@@ -1274,20 +1274,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.17,08</t>
+          <t>2.15,77</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.11.2023</t>
+          <t>14.11.2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Holmen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">

--- a/EndResult/200m Rygg.xlsx
+++ b/EndResult/200m Rygg.xlsx
@@ -572,25 +572,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brage Wetjen Sigernes</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.16,91</t>
+          <t>2.15,15</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.03.2024</t>
+          <t>12.04.2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -607,25 +607,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Simen Dahl Stensaas</t>
+          <t>Brage Wetjen Sigernes</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.17,03</t>
+          <t>2.16,91</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08.02.2015</t>
+          <t>17.03.2024</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -642,25 +642,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gleb Eriksson</t>
+          <t>Simen Dahl Stensaas</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.17,43</t>
+          <t>2.17,03</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21.05.2005</t>
+          <t>08.02.2015</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -677,25 +677,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sebastian Amundsen</t>
+          <t>Gleb Eriksson</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.17,60</t>
+          <t>2.17,43</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>26.10.2019</t>
+          <t>21.05.2005</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -712,25 +712,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Erlend Tofte Haarsaker</t>
+          <t>Sebastian Amundsen</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.17,75</t>
+          <t>2.17,60</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.01.2013</t>
+          <t>26.10.2019</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -747,25 +747,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Erlend Tofte Haarsaker</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.17,89</t>
+          <t>2.17,75</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>07.06.2025</t>
+          <t>13.01.2013</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Porsgrunn</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -782,25 +782,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Eirik Hakvåg-Sandengen</t>
+          <t>Mattias Isaksen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.18,40</t>
+          <t>2.17,75</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.01.2024</t>
+          <t>29.05.2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -873,20 +873,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.15,05</t>
+          <t>2.13,70</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>569</v>
+        <v>586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>04.07.2025</t>
+          <t>17.04.2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rud</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1113,25 +1113,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Andreas Aglen Alsos</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.27,87</t>
+          <t>2.27,35</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>23.04.2023</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1148,20 +1148,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Andreas Aglen Alsos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.28,11</t>
+          <t>2.27,87</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12.04.2024</t>
+          <t>23.04.2023</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1183,20 +1183,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jon Olav Båtbukt</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.30,64</t>
+          <t>2.28,11</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>30.05.2015</t>
+          <t>12.04.2024</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1671,15 +1671,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.23,09</t>
+          <t>2.22,63</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>05.04.2025</t>
+          <t>18.04.2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
